--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -4752,13 +4752,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="10" t="n">
         <v>0</v>
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W40" s="10" t="n">
         <v>0</v>
@@ -7200,13 +7200,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W64" s="10" t="n">
         <v>0</v>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,11 @@
       <c r="AB2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1541,7 +1545,11 @@
       <c r="AB8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1743,7 +1751,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2155,7 +2167,11 @@
       <c r="AB14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2256,7 +2272,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3690,7 +3710,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4716,7 +4740,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5532,7 +5560,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5633,7 +5665,11 @@
       <c r="AB48" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6247,7 +6283,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6655,7 +6695,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -7891,7 +7935,11 @@
       <c r="AB70" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7992,7 +8040,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8808,7 +8860,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8909,7 +8965,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9111,7 +9171,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9317,7 +9381,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -10749,7 +10817,11 @@
       <c r="AB98" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC98" s="4" t="inlineStr"/>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -11060,7 +11132,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11266,7 +11342,11 @@
       <c r="AB103" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11573,7 +11653,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11775,7 +11859,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -13225,7 +13313,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13633,7 +13725,11 @@
       <c r="AB126" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 54 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
         <v>1</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="10" t="n">
         <v>0</v>
@@ -1106,8 +1106,8 @@
       <c r="S4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="10" t="n">
-        <v>0</v>
+      <c r="T4" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="10" t="n">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="10" t="n">
         <v>0</v>
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="P51" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" s="10" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q54" s="10" t="n">
         <v>1</v>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>1</v>
@@ -6768,7 +6768,7 @@
         <v>2</v>
       </c>
       <c r="R59" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="10" t="n">
         <v>1</v>
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10095,8 +10095,8 @@
       <c r="Y91" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="10" t="n">
-        <v>0</v>
+      <c r="Z91" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="9" t="n">
         <v>1</v>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="P112" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q112" s="10" t="n">
         <v>1</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="10" t="n">
         <v>0</v>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -14963,7 +14963,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="S2" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="10" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="P6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="10" t="n">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="P15" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="10" t="n">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="U15" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15" s="10" t="n">
         <v>2</v>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="10" t="n">
         <v>1</v>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2986,8 +2986,8 @@
       <c r="Y22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="10" t="n">
-        <v>0</v>
+      <c r="Z22" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="9" t="n">
         <v>1</v>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3192,8 +3192,8 @@
       <c r="Y24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="10" t="n">
-        <v>0</v>
+      <c r="Z24" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="9" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3293,8 +3293,8 @@
       <c r="Y25" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="10" t="n">
-        <v>0</v>
+      <c r="Z25" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="9" t="n">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3394,8 +3394,8 @@
       <c r="Y26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="10" t="n">
-        <v>0</v>
+      <c r="Z26" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>1</v>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S28" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="10" t="n">
         <v>0</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="10" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3907,8 +3907,8 @@
       <c r="Y31" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="10" t="n">
-        <v>0</v>
+      <c r="Z31" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="9" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4086,8 +4086,8 @@
       <c r="P33" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="10" t="n">
-        <v>0</v>
+      <c r="Q33" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R33" s="10" t="n">
         <v>0</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4214,8 +4214,8 @@
       <c r="Y34" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="10" t="n">
-        <v>0</v>
+      <c r="Z34" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="9" t="n">
         <v>1</v>
@@ -4469,13 +4469,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="10" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4818,8 +4818,8 @@
       <c r="S40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="T40" s="10" t="n">
-        <v>0</v>
+      <c r="T40" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="10" t="n">
         <v>0</v>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5038,8 +5038,8 @@
       <c r="Y42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="10" t="n">
-        <v>0</v>
+      <c r="Z42" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="9" t="n">
         <v>1</v>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5641,8 +5641,8 @@
       <c r="T48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U48" s="10" t="n">
-        <v>0</v>
+      <c r="U48" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5734,8 +5734,8 @@
       <c r="P49" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="10" t="n">
-        <v>1</v>
+      <c r="Q49" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R49" s="10" t="n">
         <v>0</v>
@@ -5761,8 +5761,8 @@
       <c r="Y49" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="10" t="n">
-        <v>0</v>
+      <c r="Z49" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="9" t="n">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="Q51" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="10" t="n">
         <v>0</v>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6068,8 +6068,8 @@
       <c r="Y52" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="10" t="n">
-        <v>0</v>
+      <c r="Z52" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="9" t="n">
         <v>1</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6480,8 +6480,8 @@
       <c r="Y56" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="10" t="n">
-        <v>0</v>
+      <c r="Z56" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="9" t="n">
         <v>1</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6686,8 +6686,8 @@
       <c r="Y58" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="10" t="n">
-        <v>0</v>
+      <c r="Z58" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="9" t="n">
         <v>1</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7405,8 +7405,8 @@
       <c r="Y65" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="10" t="n">
-        <v>0</v>
+      <c r="Z65" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="9" t="n">
         <v>1</v>
@@ -8567,15 +8567,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>8039</v>
+        <v>4336</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Excellent Training Club</t>
+          <t>Eng Peng Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8589,76 +8589,72 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K77" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="W77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L77" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O77" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8672,15 +8668,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>4336</v>
+        <v>8039</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Keningau Mandarin Club</t>
+          <t>Excellent Training Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8694,13 +8690,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8708,11 +8704,11 @@
         </is>
       </c>
       <c r="M78" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
@@ -8721,45 +8717,49 @@
         </is>
       </c>
       <c r="P78" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q78" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="10" t="n">
-        <v>0</v>
+      <c r="S78" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V78" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="10" t="n">
-        <v>0</v>
+      <c r="X78" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="Y78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="10" t="n">
-        <v>0</v>
+      <c r="Z78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10068,8 +10068,8 @@
       <c r="P91" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" s="10" t="n">
-        <v>1</v>
+      <c r="Q91" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="10" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10200,8 +10200,8 @@
       <c r="Y92" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="10" t="n">
-        <v>0</v>
+      <c r="Z92" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="9" t="n">
         <v>1</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10886,8 +10886,8 @@
       <c r="P99" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" s="10" t="n">
-        <v>0</v>
+      <c r="Q99" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R99" s="10" t="n">
         <v>0</v>
@@ -10895,8 +10895,8 @@
       <c r="S99" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T99" s="10" t="n">
-        <v>0</v>
+      <c r="T99" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U99" s="10" t="n">
         <v>0</v>
@@ -11263,7 +11263,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11333,8 +11333,8 @@
       <c r="Y103" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>0</v>
+      <c r="Z103" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="9" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11644,8 +11644,8 @@
       <c r="Y106" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="10" t="n">
-        <v>0</v>
+      <c r="Z106" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="9" t="n">
         <v>1</v>
@@ -12145,7 +12145,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" s="10" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="P113" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>2</v>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12727,13 +12727,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>2</v>
       </c>
       <c r="V117" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="10" t="n">
         <v>0</v>
@@ -12783,8 +12783,8 @@
       <c r="Y117" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>0</v>
+      <c r="Z117" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="9" t="n">
         <v>1</v>
@@ -13234,7 +13234,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13289,8 +13289,8 @@
       <c r="T122" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="10" t="n">
-        <v>0</v>
+      <c r="U122" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="10" t="n">
         <v>0</v>
@@ -14435,7 +14435,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14501,7 +14501,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14534,7 +14534,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -14567,7 +14567,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14600,7 +14600,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14633,7 +14633,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -14699,7 +14699,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14732,7 +14732,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14765,7 +14765,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14831,7 +14831,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14897,13 +14897,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -14963,7 +14963,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14996,7 +14996,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15029,7 +15029,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15062,7 +15062,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15128,7 +15128,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15161,7 +15161,7 @@
         <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -897,8 +897,8 @@
       <c r="R2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="S2" s="10" t="n">
-        <v>1</v>
+      <c r="S2" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T2" s="10" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1002,8 +1002,8 @@
       <c r="R3" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="10" t="n">
-        <v>0</v>
+      <c r="S3" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T3" s="10" t="n">
         <v>0</v>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1200,22 +1200,22 @@
         </is>
       </c>
       <c r="P5" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V5" s="10" t="n">
         <v>3</v>
@@ -1274,17 +1274,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1480,17 +1480,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="10" t="n">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1791,17 +1791,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1896,17 +1896,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1937,8 +1937,8 @@
       <c r="T12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="10" t="n">
-        <v>0</v>
+      <c r="U12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2001,17 +2001,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
@@ -2045,8 +2045,8 @@
       <c r="U13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="10" t="n">
-        <v>2</v>
+      <c r="V13" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="10" t="n">
         <v>0</v>
@@ -2102,17 +2102,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W14" s="10" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2207,17 +2207,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="P15" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="10" t="n">
         <v>0</v>
@@ -2251,8 +2251,8 @@
       <c r="U15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="V15" s="10" t="n">
-        <v>2</v>
+      <c r="V15" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="10" t="n">
         <v>0</v>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="7" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2724,17 +2724,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="7" t="n">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2974,11 +2974,11 @@
       <c r="U22" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="10" t="n">
-        <v>0</v>
+      <c r="V22" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>0</v>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W23" s="10" t="n">
         <v>0</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" s="10" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3443,13 +3443,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="10" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" s="10" t="n">
         <v>0</v>
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" s="10" t="n">
         <v>0</v>
@@ -3952,17 +3952,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4158,13 +4158,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="10" t="n">
         <v>0</v>
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4469,13 +4469,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L37" s="8" t="inlineStr">
         <is>
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="X39" s="9" t="n">
         <v>5</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>KITA</t>
+          <t>KITA INTERNATIONAL TOASTMASTERS CLUB</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
@@ -4881,13 +4881,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5026,11 +5026,11 @@
       <c r="U42" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="10" t="n">
-        <v>0</v>
+      <c r="V42" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W42" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="X42" s="9" t="n">
         <v>4</v>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X44" s="9" t="n">
         <v>5</v>
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5419,8 +5419,8 @@
       <c r="P46" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" s="10" t="n">
-        <v>1</v>
+      <c r="Q46" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="R46" s="10" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5600,17 +5600,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="P50" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="10" t="n">
         <v>1</v>
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W51" s="10" t="n">
         <v>0</v>
@@ -6012,13 +6012,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6265,8 +6265,8 @@
       <c r="V54" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="W54" s="10" t="n">
-        <v>1</v>
+      <c r="W54" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="X54" s="9" t="n">
         <v>6</v>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6529,13 +6529,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="10" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W58" s="10" t="n">
         <v>0</v>
@@ -6735,17 +6735,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
@@ -6783,7 +6783,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>1</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="8" t="inlineStr">
         <is>
@@ -7450,17 +7450,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7599,11 +7599,11 @@
       <c r="U67" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="10" t="n">
-        <v>3</v>
+      <c r="V67" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67" s="9" t="n">
         <v>5</v>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7765,13 +7765,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7806,8 +7806,8 @@
       <c r="T69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U69" s="10" t="n">
-        <v>0</v>
+      <c r="U69" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V69" s="10" t="n">
         <v>0</v>
@@ -7870,13 +7870,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7975,13 +7975,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>11</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="P71" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="10" t="n">
         <v>0</v>
@@ -8023,7 +8023,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X71" s="9" t="n">
         <v>7</v>
@@ -8080,13 +8080,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="8" t="inlineStr">
         <is>
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W73" s="10" t="n">
         <v>0</v>
@@ -8282,13 +8282,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8387,13 +8387,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -8589,13 +8589,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8690,13 +8690,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8795,17 +8795,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="7" t="n">
@@ -8833,14 +8833,14 @@
       <c r="S79" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="10" t="n">
-        <v>0</v>
+      <c r="T79" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V79" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="10" t="n">
         <v>0</v>
@@ -8900,17 +8900,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -9005,13 +9005,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9106,17 +9106,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="7" t="n">
@@ -9211,17 +9211,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="7" t="n">
@@ -9421,17 +9421,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9627,13 +9627,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9776,11 +9776,11 @@
       <c r="U88" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="10" t="n">
-        <v>0</v>
+      <c r="V88" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="9" t="n">
         <v>5</v>
@@ -9938,13 +9938,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="8" t="inlineStr">
         <is>
@@ -10039,17 +10039,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="7" t="n">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10144,13 +10144,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="8" t="inlineStr">
         <is>
@@ -10170,26 +10170,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P92" s="10" t="n">
+      <c r="P92" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" s="10" t="n">
-        <v>0</v>
       </c>
       <c r="W92" s="10" t="n">
         <v>0</v>
@@ -10445,13 +10445,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10752,13 +10752,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10796,11 +10796,11 @@
       <c r="U98" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="10" t="n">
-        <v>0</v>
+      <c r="V98" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>7</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10857,13 +10857,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10901,11 +10901,11 @@
       <c r="U99" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="10" t="n">
-        <v>0</v>
+      <c r="V99" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="9" t="n">
         <v>7</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10962,13 +10962,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11006,11 +11006,11 @@
       <c r="U100" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="10" t="n">
-        <v>0</v>
+      <c r="V100" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X100" s="9" t="n">
         <v>7</v>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11111,11 +11111,11 @@
       <c r="U101" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="10" t="n">
-        <v>0</v>
+      <c r="V101" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X101" s="9" t="n">
         <v>7</v>
@@ -11172,13 +11172,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11321,8 +11321,8 @@
       <c r="U103" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="10" t="n">
-        <v>0</v>
+      <c r="V103" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="10" t="n">
         <v>0</v>
@@ -11382,13 +11382,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -11483,17 +11483,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="7" t="n">
@@ -11588,13 +11588,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="10" t="n">
         <v>0</v>
@@ -11794,17 +11794,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11899,13 +11899,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -12004,17 +12004,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="7" t="n">
@@ -12109,17 +12109,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="7" t="n">
@@ -12214,17 +12214,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
@@ -12250,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="10" t="n">
         <v>0</v>
@@ -12319,13 +12319,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12521,13 +12521,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12565,11 +12565,11 @@
       <c r="U115" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" s="10" t="n">
-        <v>0</v>
+      <c r="V115" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W115" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="X115" s="9" t="n">
         <v>6</v>
@@ -12727,13 +12727,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>2</v>
       </c>
       <c r="V117" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="10" t="n">
         <v>0</v>
@@ -12828,17 +12828,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
@@ -12933,17 +12933,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -13038,13 +13038,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -13143,17 +13143,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -13248,17 +13248,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -13353,17 +13353,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -13458,13 +13458,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -13559,13 +13559,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L125" s="8" t="inlineStr">
         <is>
@@ -13660,17 +13660,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -13765,17 +13765,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13870,17 +13870,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13975,13 +13975,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -14080,13 +14080,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -14351,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -14384,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -14402,7 +14402,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -14417,7 +14417,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -14435,7 +14435,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14450,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14483,7 +14483,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -14501,7 +14501,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14582,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -14633,7 +14633,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -14666,7 +14666,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14714,7 +14714,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14732,7 +14732,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14780,7 +14780,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -14831,7 +14831,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14846,7 +14846,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -14897,7 +14897,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -14912,7 +14912,7 @@
         <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -14945,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -14963,7 +14963,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14978,7 +14978,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14996,7 +14996,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15029,13 +15029,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -15062,7 +15062,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15077,7 +15077,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -15110,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -15128,7 +15128,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15143,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -15176,7 +15176,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -15209,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -894,8 +894,8 @@
       <c r="Q2" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R2" s="10" t="n">
-        <v>1</v>
+      <c r="R2" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S2" s="9" t="n">
         <v>2</v>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2143,11 +2143,11 @@
       <c r="T14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="10" t="n">
-        <v>0</v>
+      <c r="U14" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" s="10" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2251,8 +2251,8 @@
       <c r="U15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>4</v>
+      <c r="V15" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="W15" s="10" t="n">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="10" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="10" t="n">
         <v>0</v>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4675,13 +4675,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X39" s="9" t="n">
         <v>5</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="P44" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="10" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
         <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X44" s="9" t="n">
         <v>5</v>
@@ -5390,13 +5390,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V46" s="10" t="n">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W51" s="10" t="n">
         <v>0</v>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="10" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="10" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6770,8 +6770,8 @@
       <c r="R59" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="S59" s="10" t="n">
-        <v>1</v>
+      <c r="S59" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="T59" s="10" t="n">
         <v>0</v>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7698,8 +7698,8 @@
       <c r="S68" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="10" t="n">
-        <v>0</v>
+      <c r="T68" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="10" t="n">
         <v>0</v>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="P71" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q71" s="10" t="n">
         <v>0</v>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="P72" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="10" t="n">
         <v>1</v>
@@ -8121,8 +8121,8 @@
       <c r="T72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="U72" s="10" t="n">
-        <v>0</v>
+      <c r="U72" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="V72" s="10" t="n">
         <v>1</v>
@@ -8942,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="U80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V80" s="9" t="n">
         <v>4</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9316,13 +9316,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9360,8 +9360,8 @@
       <c r="U84" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="10" t="n">
-        <v>3</v>
+      <c r="V84" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="10" t="n">
         <v>0</v>
@@ -9526,13 +9526,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="10" t="n">
         <v>0</v>
@@ -10445,13 +10445,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -12214,13 +12214,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>4</v>
       </c>
       <c r="W112" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X112" s="9" t="n">
         <v>7</v>
@@ -12355,7 +12355,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T113" s="10" t="n">
         <v>0</v>
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12458,8 +12458,8 @@
       <c r="S114" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="10" t="n">
-        <v>0</v>
+      <c r="T114" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U114" s="10" t="n">
         <v>0</v>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -14438,10 +14438,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -14765,13 +14765,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -14831,7 +14831,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -14930,7 +14930,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15128,7 +15128,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/87/inyear.xlsx
+++ b/docs/d/87/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -900,8 +900,8 @@
       <c r="S2" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T2" s="10" t="n">
-        <v>0</v>
+      <c r="T2" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U2" s="10" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>0</v>
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="P32" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="10" t="n">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="10" t="n">
         <v>0</v>
@@ -6204,7 +6204,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6247,14 +6247,14 @@
       <c r="P54" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="Q54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" s="10" t="n">
-        <v>0</v>
+      <c r="Q54" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" s="9" t="n">
         <v>1</v>
@@ -6735,17 +6735,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
@@ -6783,7 +6783,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="P73" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="10" t="n">
         <v>1</v>
@@ -8828,10 +8828,10 @@
         <v>2</v>
       </c>
       <c r="R79" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="9" t="n">
         <v>1</v>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L80" s="8" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="P82" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="10" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9459,8 +9459,8 @@
       <c r="S85" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="T85" s="10" t="n">
-        <v>0</v>
+      <c r="T85" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="10" t="n">
         <v>0</v>
@@ -10039,13 +10039,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -10445,13 +10445,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="P103" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="10" t="n">
         <v>0</v>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -14732,7 +14732,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -14780,7 +14780,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -14930,7 +14930,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
